--- a/LinkedIn/linkedin_jobs.xlsx
+++ b/LinkedIn/linkedin_jobs.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +490,11 @@
           <t>Apply link</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Easy Apply</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +541,7 @@
           <t>https://www.linkedin.com/jobs/search/?currentJobId=4455873041&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -581,6 +588,7 @@
           <t>https://www.linkedin.com/jobs/search/?currentJobId=4458132764&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -619,6 +627,7 @@
           <t>https://www.linkedin.com/jobs/search/?currentJobId=4458178209&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -665,6 +674,7 @@
           <t>https://www.linkedin.com/jobs/search/?currentJobId=4455841170&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -705,6 +715,199 @@
       <c r="J6" s="1" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/search/?currentJobId=4458193505&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>react, javascript, tailwind css, tailwind, bootstrap, java, git, github</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wake Up Whistle</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Within 7d (search filter)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LinkedIn (Playwright)</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?currentJobId=4456887166&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>react, typescript, javascript, redux, java, git</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Frontend Developer - TypeScript (Remote)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quik Hire Staffing</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>$30 - $80</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Within 7d (search filter)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LinkedIn (Playwright)</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?currentJobId=4458153590&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>javascript, java, python</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Web Developer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CareerXperts Consulting</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1 - 2 years</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 - 2 </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Within 7d (search filter)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LinkedIn (Playwright)</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?currentJobId=4455867426&amp;f_TPR=r604800&amp;keywords=Frontend%20React%20Bengaluru</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>react, next.js, typescript, javascript, redux, zustand, java, git, financial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Senior React Developer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sa.global</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>senior</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Within 7d (search filter)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LinkedIn (Playwright)</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?currentJobId=4447283793&amp;f_TPR=r604800&amp;keywords=React%20TypeScript%20Bengaluru</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -715,6 +918,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
